--- a/docs/지도자_DB.xlsx
+++ b/docs/지도자_DB.xlsx
@@ -2825,7 +2825,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>버전 v1.45.0</t>
+          <t>버전 v1.46.0</t>
         </is>
       </c>
     </row>

--- a/docs/지도자_DB.xlsx
+++ b/docs/지도자_DB.xlsx
@@ -2825,7 +2825,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>버전 v1.46.0</t>
+          <t>버전 v1.47.0</t>
         </is>
       </c>
     </row>
